--- a/public/reports/kashyap-pavra-audience-intelligence-june-2026.xlsx
+++ b/public/reports/kashyap-pavra-audience-intelligence-june-2026.xlsx
@@ -643,14 +643,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -689,17 +689,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bagher Ahmadi</t>
+          <t>Aishwarya Puranik</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Co-founder, iWAND | Agentic AI Stylist for Shopify Fashion</t>
+          <t>Marketing Manager | Brand Strategy | Luxury Retail Marketing</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>iWAND</t>
+          <t>Luxury Retail</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -709,29 +709,29 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Shopify AI / Fashion</t>
+          <t>Brand manager / Luxury retail</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Direct ICP signal. AI styling for Shopify fashion sits exactly at the intersection of premium commerce, fashion, product experience and conversion.</t>
+          <t>Brand managers are a priority ICP because they own perception, product storytelling and premium buying behaviour. Her viewing signals Kashyap's design-trust angle is reaching people who care about brand quality, not cheap execution.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aishwarya Puranik</t>
+          <t>Khayelihle Ntaka</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Marketing Manager | Brand Strategy | Luxury Retail Marketing</t>
+          <t>Founder @ Command Ledger</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Luxury Retail</t>
+          <t>Command Ledger</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -741,31 +741,27 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Luxury retail / Brand</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Luxury retail cares about taste, perception, visual trust and premium buying behaviour. This is the audience Kashyap needs for high-ticket Shopify work.</t>
+          <t>Founder attention matters because founders buy judgment and outcomes. This is the kind of viewer who may not need a Shopify build today, but can become a buyer, referrer or strategic connector.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Khayelihle Ntaka</t>
+          <t>Marco Ciaccia</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Founder @ Command Ledger</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Command Ledger</t>
-        </is>
-      </c>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -778,26 +774,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Founder attention matters because founders buy judgment, not just implementation. A founder viewer is a possible buyer, referrer or strategic connector.</t>
+          <t>Founder viewers are high-value because they benchmark operators and agencies before a need becomes public. This is the commercial audience Kashyap should quietly warm up.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Someone at Lieblingsgarn GmbH</t>
+          <t>Romiluyi Abiodun</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Company viewer</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Lieblingsgarn GmbH</t>
-        </is>
-      </c>
+          <t>Founder &amp; Creative Director</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -805,31 +797,27 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>E-commerce brand</t>
+          <t>Founder / Creative partner</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Brand-side company viewer. More commercially useful than broad practitioner attention because this can become a direct lead.</t>
+          <t>Founder plus creative direction is a strong fit for premium brand work. This person understands design as business value, which matches Kashyap's positioning.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Someone at Refactor Plus</t>
+          <t>Jolene Henkeman</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Shopify agency viewer</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Refactor Plus</t>
-        </is>
-      </c>
+          <t>Email &amp; Ads Marketing | eCommerce customer acquisition</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -837,27 +825,31 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Shopify ecosystem</t>
+          <t>Ad / Growth partner</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Agency/ecosystem attention means Kashyap is being watched inside the category where referrals and comparisons happen.</t>
+          <t>Ad and retention partners are valuable ICP-adjacent viewers. They sit close to the same e-commerce revenue problem: traffic is expensive, so the Shopify experience has to convert.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Yash P Y</t>
+          <t>Prachi Kumar</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Scaling Shopify Brands Through CRO, Custom Development &amp; Growth Strategy</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
+          <t>Partnerships @ OneXtel | WhatsApp, RCS &amp; SMS growth</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>OneXtel</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -865,31 +857,27 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Shopify / CRO</t>
+          <t>Brand partner / Commerce comms</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Direct category fit: Shopify, CRO, custom development and growth strategy. This viewer validates the exact positioning lane.</t>
+          <t>Commerce messaging and partnership leaders can become referral partners. They understand owned-channel growth and can carry Kashyap into conversations with brands.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Someone at Wellness Extract</t>
+          <t>Gita Sinha</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Company viewer</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Wellness Extract</t>
-        </is>
-      </c>
+          <t>Online PR and corporate image management</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -897,29 +885,29 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Wellness commerce</t>
+          <t>Brand partner / PR</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Wellness is a strong Shopify/D2C category. A company-level viewer is a possible buyer signal, especially when Kashyap is writing about premium product pages and trust.</t>
+          <t>PR and image-management viewers are relevant because premium Shopify is partly a trust problem. This profile validates that Kashyap's content is crossing into brand reputation territory.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Someone at Duck.design</t>
+          <t>Bagher Ahmadi</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Company viewer</t>
+          <t>Co-founder, iWAND | Agentic AI Stylist for Shopify Fashion</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Duck.design</t>
+          <t>iWAND</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -929,108 +917,108 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Design / Commerce</t>
+          <t>Founder / AI commerce</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Design-company attention matters because Kashyap's premium Shopify positioning depends on taste, conversion and visual authority.</t>
+          <t>AI styling for Shopify fashion sits at the intersection of commerce, fashion and conversion. This is exactly the sort of founder/operator category Kashyap should be visible to.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Yash P Y</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Scaling Shopify Brands Through CRO, Custom Development &amp; Growth Strategy</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Shopify partner / CRO</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Shopify CRO partners are not always buyers, but they are strong champions. They can validate Kashyap's thinking and create referrals inside the same category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Sagar Vaghela</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Senior Shopify Designer | CRO-focused design</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Shopify design / CRO</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>This is a direct category signal. Shopify design and CRO specialists watching Kashyap means his authority is landing inside the same buying and referral ecosystem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Marco Ciaccia</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Founder viewers matter because they can buy, refer, or benchmark Kashyap against alternatives. This is higher-value attention than broad creator engagement.</t>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Shopify designer / CRO</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>A senior Shopify designer is a useful peer signal. This audience understands the craft and can help Kashyap build category credibility.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Romiluyi Abiodun</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Founder &amp; Creative Director</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Founder / Creative</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Founder plus creative direction is a strong signal for premium brand work. This audience cares about design judgment, not only development.</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Senior Technical Lead | Shopify &amp; Full-Stack Expert</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Shopify technical partner</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Senior Shopify technical viewers are useful champions. They may not buy, but they can validate technical judgment and amplify Kashyap's authority among implementation partners.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Aftab Pathan</t>
+          <t>Ankur Singh S</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Frontend Engineer | React.js, Next.js, TypeScript</t>
+          <t>Shopify Developer | Liquid, custom sections, theme customization</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -1041,31 +1029,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Technical champion</t>
+          <t>Shopify developer</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Technical viewer who understands implementation quality. Useful champion layer for Shopify build credibility.</t>
+          <t>Shopify developers are ecosystem amplifiers. They matter because they understand whether Kashyap's ideas are technically credible.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Anushk Goel</t>
+          <t>Hardik Rathavi</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>IP Consultant at GreyB | Supporting IP Strategy</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>GreyB</t>
-        </is>
-      </c>
+          <t>Bubble.io Certified | Shopify | Laravel Developer</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Tier 2</t>
@@ -1073,24 +1057,24 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Strategy / Research</t>
+          <t>Developer / Shopify adjacent</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Adjacent strategy viewer. Useful because premium brands also care about IP, differentiation and defensible assets.</t>
+          <t>Developer attention matters when Kashyap talks about quality and implementation. This is a peer/champion segment, not the main buyer group.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Gita Sinha</t>
+          <t>Aftab Pathan</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Online PR and corporate image management</t>
+          <t>Frontend Engineer | React.js, Next.js, TypeScript</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -1101,27 +1085,31 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>PR / Brand</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Brand reputation viewer. Fits the premium-positioning side of Kashyap's content.</t>
+          <t>Frontend engineers are useful because premium Shopify depends on performance, interface and implementation quality. This is a technical champion signal.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Jolene Henkeman</t>
+          <t>Chintan Raval</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Email &amp; Ads Marketing | eCommerce customer acquisition</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
+          <t>Driving SaaS revenue | Account Executive at SwiftSku</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>SwiftSku</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Tier 2</t>
@@ -1129,29 +1117,29 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>E-commerce marketing</t>
+          <t>SaaS GTM / Commerce tech</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>E-commerce marketers are champion profiles. They may not own the website budget alone, but they influence conversion, retention and campaign performance conversations.</t>
+          <t>Commerce-SaaS GTM people can become connectors. They understand the revenue problem around stores, tools and conversion, even if they are not the direct buyer.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Prachi Kumar</t>
+          <t>Anth Walker</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Partnerships @ OneXtel | WhatsApp, RCS &amp; SMS growth</t>
+          <t>Director of Finance at Visualsoft</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>OneXtel</t>
+          <t>Visualsoft</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1161,116 +1149,112 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Partnerships / Commerce comms</t>
+          <t>Commerce software operator</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Partnerships and messaging leaders sit close to commerce growth. This is useful ecosystem reach for brands that sell through owned channels.</t>
+          <t>Finance leadership at an e-commerce/software company is a useful commercial signal because budget, margin and growth all connect to conversion work.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Anth Walker</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Director of Finance at Visualsoft</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Visualsoft</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>E-commerce finance</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Finance leadership at an e-commerce/software company is a practical business signal: people around budget, growth and margin are seeing the account.</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Anushk Goel</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>IP Consultant at GreyB | Supporting IP Strategy</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>GreyB</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Strategy / Research</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>This is not core Shopify ICP, but it suggests Kashyap's positioning touches defensibility, category language and differentiation.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Chintan Raval</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Driving SaaS revenue | Account Executive at SwiftSku</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>SwiftSku</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>SaaS GTM</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>GTM viewers in commerce software can become connectors. They understand the buyer pain and can carry Kashyap's name into SaaS/e-commerce conversations.</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Fakhruddin KW</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer | .NET, SQL, SPFx, SharePoint, Power BI, Azure</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Tech practitioner</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Not a direct buyer, but technical practitioners widen software-community reach and add credibility around implementation themes.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Dinesh Kumar</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Senior Technical Lead | Shopify &amp; Full-Stack Expert</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Shopify technical</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Senior Shopify technical viewers are credibility validators. They may not be buyers, but they can validate Kashyap's technical judgment publicly or through referrals.</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Meda Riya Reddy</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning enthusiast | Deep Learning, NLP, Computer Vision</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>AI practitioner</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>AI practitioners expand reach around AI and product quality. Useful for awareness, but less important than founders, brand managers and Shopify partners.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Fakhruddin KW</t>
+          <t>Gyorgy Richard Kiss</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Software Developer | .NET, SQL, SPFx, SharePoint, Power BI, Azure</t>
+          <t>Business Development &amp; Client Partnership Manager</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr"/>
@@ -1281,24 +1265,24 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Tech practitioner</t>
+          <t>BD / Recruitment</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Not direct buyer, but technical practitioners amplify credibility and widen software-community reach.</t>
+          <t>Adjacent business-development reach. Useful for network spread, but not a core Shopify buyer signal.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>A recruiter</t>
+          <t>Daniel Dramshev</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Recruiter profile viewer</t>
+          <t>HVAC Marketing Consultant</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
@@ -1309,24 +1293,24 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Recruiter / Talent</t>
+          <t>Adjacent marketing</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Recruiters are not the primary ICP, but they show Kashyap is being discovered by adjacent professional networks.</t>
+          <t>Cross-industry marketing attention shows the ideas are understandable beyond Shopify, but this is not a priority buyer segment.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Meda Riya Reddy</t>
+          <t>Anza Javaid</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning enthusiast | Deep Learning, NLP, Computer Vision</t>
+          <t>Lead 3D Artist | AI + 3D workflows for video production</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
@@ -1337,24 +1321,24 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>AI practitioner</t>
+          <t>Creative / AI</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>AI practitioners expand topic reach around AI and product quality. Useful for reach, less useful as a direct buyer signal.</t>
+          <t>Creative AI attention supports the visual-quality theme, but it is an ecosystem signal rather than a direct commercial ICP.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Gyorgy Richard Kiss</t>
+          <t>Ibraheem Rashid</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Business Development &amp; Client Partnership Manager</t>
+          <t>Senior Business Development Professional</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
@@ -1365,278 +1349,42 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BD / Recruitment</t>
+          <t>BD / Partnerships</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Adjacent business-development reach. Useful for network spread, but not a core Shopify buyer signal.</t>
+          <t>Partnership viewers can spread the content, but this profile is more connector than buyer for Kashyap's offer.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Daniel Dramshev</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>HVAC Marketing Consultant</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Adjacent marketing</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>A cross-industry marketing viewer shows the ideas are understandable beyond Shopify, but this is not a priority buyer segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Anza Javaid</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Lead 3D Artist | AI + 3D workflows for video production</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Creative / AI</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Creative AI attention supports the visual-quality theme, but it is an ecosystem signal rather than a direct commercial ICP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Ibraheem Rashid</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Senior Business Development Professional</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BD / Partnerships</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Partnership viewers can spread the content, but this profile is more connector than buyer for Kashyap's offer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Hardik Rathavi</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Bubble.io Certified | Shopify | Laravel Developer</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Developer attention helps with technical credibility and peer validation, but it is not the main buyer group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Ankur Singh S</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Shopify Developer | Liquid, custom sections, theme customization</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Shopify developer</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Shopify developers are ecosystem amplifiers. They can validate craft, but the commercial priority remains founders and brand-side teams.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Someone at ZEPIC</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Company viewer</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>ZEPIC</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Company viewer</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Useful as a company-level signal, but the screenshot does not give enough role context to treat it as a direct ICP buyer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Product Manager at Baidu</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Product Manager</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Baidu</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Product / Tech</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Strong tech credibility signal, but not a direct Shopify buyer unless future context reveals commerce ownership.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Project Manager in IT Services</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>IT services</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Project-management viewers broaden the technical audience, but this is weaker than founder, brand, or Shopify-specific attention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Tanisha Venkani</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Internal agency profile</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>The Right Click Projects</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Exclude</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Internal viewer. Do not treat as client-facing audience signal.</t>
         </is>
@@ -1653,14 +1401,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1699,17 +1447,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bagher Ahmadi</t>
+          <t>Aishwarya Puranik</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Co-founder, iWAND | Agentic AI Stylist for Shopify Fashion</t>
+          <t>Marketing Manager | Brand Strategy | Luxury Retail Marketing</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>iWAND</t>
+          <t>Luxury Retail</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1719,29 +1467,29 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Shopify AI / Fashion</t>
+          <t>Brand manager / Luxury retail</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Direct ICP signal. AI styling for Shopify fashion sits exactly at the intersection of premium commerce, fashion, product experience and conversion.</t>
+          <t>Brand managers are a priority ICP because they own perception, product storytelling and premium buying behaviour. Her viewing signals Kashyap's design-trust angle is reaching people who care about brand quality, not cheap execution.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aishwarya Puranik</t>
+          <t>Khayelihle Ntaka</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Marketing Manager | Brand Strategy | Luxury Retail Marketing</t>
+          <t>Founder @ Command Ledger</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Luxury Retail</t>
+          <t>Command Ledger</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1751,31 +1499,27 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Luxury retail / Brand</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Luxury retail cares about taste, perception, visual trust and premium buying behaviour. This is the audience Kashyap needs for high-ticket Shopify work.</t>
+          <t>Founder attention matters because founders buy judgment and outcomes. This is the kind of viewer who may not need a Shopify build today, but can become a buyer, referrer or strategic connector.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Khayelihle Ntaka</t>
+          <t>Marco Ciaccia</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Founder @ Command Ledger</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Command Ledger</t>
-        </is>
-      </c>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -1788,26 +1532,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Founder attention matters because founders buy judgment, not just implementation. A founder viewer is a possible buyer, referrer or strategic connector.</t>
+          <t>Founder viewers are high-value because they benchmark operators and agencies before a need becomes public. This is the commercial audience Kashyap should quietly warm up.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Someone at Lieblingsgarn GmbH</t>
+          <t>Romiluyi Abiodun</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Company viewer</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Lieblingsgarn GmbH</t>
-        </is>
-      </c>
+          <t>Founder &amp; Creative Director</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -1815,31 +1555,27 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>E-commerce brand</t>
+          <t>Founder / Creative partner</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Brand-side company viewer. More commercially useful than broad practitioner attention because this can become a direct lead.</t>
+          <t>Founder plus creative direction is a strong fit for premium brand work. This person understands design as business value, which matches Kashyap's positioning.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Someone at Refactor Plus</t>
+          <t>Jolene Henkeman</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Shopify agency viewer</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Refactor Plus</t>
-        </is>
-      </c>
+          <t>Email &amp; Ads Marketing | eCommerce customer acquisition</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -1847,27 +1583,31 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Shopify ecosystem</t>
+          <t>Ad / Growth partner</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Agency/ecosystem attention means Kashyap is being watched inside the category where referrals and comparisons happen.</t>
+          <t>Ad and retention partners are valuable ICP-adjacent viewers. They sit close to the same e-commerce revenue problem: traffic is expensive, so the Shopify experience has to convert.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Yash P Y</t>
+          <t>Prachi Kumar</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Scaling Shopify Brands Through CRO, Custom Development &amp; Growth Strategy</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
+          <t>Partnerships @ OneXtel | WhatsApp, RCS &amp; SMS growth</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>OneXtel</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -1875,31 +1615,27 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Shopify / CRO</t>
+          <t>Brand partner / Commerce comms</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Direct category fit: Shopify, CRO, custom development and growth strategy. This viewer validates the exact positioning lane.</t>
+          <t>Commerce messaging and partnership leaders can become referral partners. They understand owned-channel growth and can carry Kashyap into conversations with brands.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Someone at Wellness Extract</t>
+          <t>Gita Sinha</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Company viewer</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Wellness Extract</t>
-        </is>
-      </c>
+          <t>Online PR and corporate image management</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -1907,29 +1643,29 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Wellness commerce</t>
+          <t>Brand partner / PR</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Wellness is a strong Shopify/D2C category. A company-level viewer is a possible buyer signal, especially when Kashyap is writing about premium product pages and trust.</t>
+          <t>PR and image-management viewers are relevant because premium Shopify is partly a trust problem. This profile validates that Kashyap's content is crossing into brand reputation territory.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Someone at Duck.design</t>
+          <t>Bagher Ahmadi</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Company viewer</t>
+          <t>Co-founder, iWAND | Agentic AI Stylist for Shopify Fashion</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Duck.design</t>
+          <t>iWAND</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1939,96 +1675,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Design / Commerce</t>
+          <t>Founder / AI commerce</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Design-company attention matters because Kashyap's premium Shopify positioning depends on taste, conversion and visual authority.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Sagar Vaghela</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Senior Shopify Designer | CRO-focused design</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Shopify design / CRO</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>This is a direct category signal. Shopify design and CRO specialists watching Kashyap means his authority is landing inside the same buying and referral ecosystem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Marco Ciaccia</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Founder viewers matter because they can buy, refer, or benchmark Kashyap against alternatives. This is higher-value attention than broad creator engagement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Romiluyi Abiodun</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Founder &amp; Creative Director</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Founder / Creative</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Founder plus creative direction is a strong signal for premium brand work. This audience cares about design judgment, not only development.</t>
+          <t>AI styling for Shopify fashion sits at the intersection of commerce, fashion and conversion. This is exactly the sort of founder/operator category Kashyap should be visible to.</t>
         </is>
       </c>
     </row>
